--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1118,6 +1118,51 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>切片-0002 验收通过；存档层补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-18 01:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>封存归档</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>快照-0001</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>证据-0007</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>归档包 197 份文件；SHA256 与 27 记录一致；标签 tm-v3.4 已推送到远端</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1164,49 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>归档包 197 份文件；SHA256 与 27 记录一致；标签 tm-v3.4 已推送到远端</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-18 01:55:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>改动-0005</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>附录B版本历史排序已提交；用于对外交付包</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1168,54 +1168,708 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-10-18 01:55:00 +08:00</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>guozhizhuang</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>提交改动</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>改动-0005</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>信息</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>附录B版本历史排序已提交；用于对外交付包</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>开启切片</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>开启切片-0003：协议全角色全开、零配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>决策-0006,决策-0007</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>v3.5 两项决策（见 28-决策记录）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>冻结契约</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>契约-0004,契约-0005</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>冻结全开与交付包两条验收标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>门禁 G0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>证据-0008,证据-0009</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>37 份编号交付物 + 3 份清单齐全；模板 40 份枚举对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>门禁 G1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>提交作者 guozhizhuang = 负责人；路径落在 TEAMODEL.md 与 协作/**</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>门禁 G2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CONTRACT.md 冻结摘要 sha256 ee70e82f…20a0 未变</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>门禁 G3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>证据-0009</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>需求-0003 全字段可追（36-追溯矩阵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>代码评审</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>门禁 G4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A-01..A-10 全 APPROVE（16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>专项评审</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>门禁 G5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>证据-0009</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>B-01..B-08 全 PASS（18）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>门禁 G6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>证据-0011</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>门禁 G7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>22-集成记录 已登记 3f1aef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>运行门禁</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>门禁 G8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>证据-0010,证据-0011</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>发布-0001 可交付；快照-0002 还原验证通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>最终验收</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>证据-0008,证据-0009,证据-0010,证据-0011</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>切片-0003 验收通过；协议 v3.5 生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>封存归档</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>快照-0002</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>归档包 215 份文件；SHA256 与 27 记录一致；标签 tm-v3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>改动-0006</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>协议与模板改动已提交（3f1aef4）</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"负责人,产品,需求分析,架构契约,实现工程师,代码评审,专项评审,测试验证,集成发布"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="H2:H121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,不完整,信息"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1861,6 +1861,141 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>协议与模板改动已提交（3f1aef4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:10:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>生成证据</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>证据-0008,证据-0009,证据-0010,证据-0011</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>v3.5 校验、齐全性、快照还原、测试与验收实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:15:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>改动-0007</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>全开档案与证据已提交（77fb43c）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>记录归档</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>快照-0002</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>打标签 tm-v3.5，归档快照记录完成</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1168,10 +1168,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1996,6 +1994,136 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>打标签 tm-v3.5，归档快照记录完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>开启切片</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>把协议与模板外置到 TEAMODEL 仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>决策-0008</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>协议与模板独立成仓，DCG 只引用</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>移除文件</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md;协作/模板/**;docs/TEAMODEL_draft_v1.md</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>DCG 版本库不再包含协议与模板</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2124,6 +2124,96 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>DCG 版本库不再包含协议与模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:55:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>改动-0008</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>协议与模板外置：DCG 提交 0436ca2，协议仓库 tag tm-v3.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:05:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>封存归档</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>快照-0003</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>证据-0013</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>归档包 179 份文件；SHA256 与 27 记录一致</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2214,6 +2214,141 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>归档包 179 份文件；SHA256 与 27 记录一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:00:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>开启切片</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>证据-0014</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>README 修订：标题 DCG、删除 v2 状态段、定位改适配场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:15:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>改动-0009</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>证据-0014</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>README.md 已提交（cbe8fbe）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>最终验收</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>验收-0009</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>证据-0014</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
         </is>
       </c>
     </row>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2347,6 +2347,141 @@
         </is>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:25:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>开启切片</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>证据-0015</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>README 写明：JSONata 是结构描述语言、编译成固化 Python 提效、主场景为任意数据结构转换</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:35:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>改动-0010</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>证据-0015</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>README.md 已提交（7c4760d）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>最终验收</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>验收-0010</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>证据-0015</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
         </is>

--- a/协作/25-账本.xlsx
+++ b/协作/25-账本.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2482,6 +2482,141 @@
         </is>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:45:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>开启切片</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>证据-0016</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>README 删除基线/修订锚点段与 §0.1–§0.3 三个子节，§0 只保留主场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:52:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>提交改动</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>改动-0011</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>证据-0016</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>README.md 已提交（ba1410d）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:55:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>最终验收</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>验收-0011</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>证据-0016</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>pytest 696 passed；accept 16 PASS / 0 FAIL / 0 SKIP</t>
         </is>
